--- a/data/export/2026-10-24-operations.xlsx
+++ b/data/export/2026-10-24-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -442,7 +442,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
@@ -643,32 +643,36 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -676,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -700,33 +704,37 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -759,32 +767,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -792,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -816,33 +828,37 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -875,32 +891,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -908,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -932,33 +952,37 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -991,32 +1015,36 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1024,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1048,33 +1076,37 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1172,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1179,7 +1211,7 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
@@ -1190,7 +1222,7 @@
       <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1288,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1338,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1404,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1454,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1520,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1538,7 +1570,7 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1636,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1654,35 +1686,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1715,12 +1747,12 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1766,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1770,35 +1802,35 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1831,12 +1863,12 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1882,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1875,46 +1907,50 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1947,12 +1983,12 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +2002,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1991,46 +2027,50 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2063,12 +2103,12 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2122,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2107,46 +2147,50 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2223,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2242,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2234,35 +2278,35 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2295,12 +2339,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2358,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2339,7 +2383,7 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2350,35 +2394,35 @@
       <c r="AC16" s="2" t="inlineStr"/>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2411,12 +2455,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2474,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2455,18 +2499,22 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2479,22 +2527,22 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2527,12 +2575,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2546,7 +2594,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2582,7 +2630,7 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -2595,22 +2643,22 @@
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2643,12 +2691,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2662,7 +2710,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2698,35 +2746,35 @@
       <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2764,7 +2812,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2778,7 +2826,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2814,35 +2862,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2880,7 +2928,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2894,7 +2942,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2930,35 +2978,35 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2996,7 +3044,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3010,7 +3058,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3046,7 +3094,3043 @@
       <c r="AC22" s="2" t="inlineStr"/>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>2/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-24-operations.xlsx
+++ b/data/export/2026-10-24-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD48"/>
+  <dimension ref="A1:AD73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1025,24 +1025,24 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1101,12 +1101,12 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1139,32 +1139,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1172,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1196,17 +1200,17 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1216,13 +1220,17 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1263,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -1288,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1312,33 +1324,37 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1371,32 +1387,36 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1404,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1428,33 +1448,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1511,36 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1520,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1544,33 +1572,37 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1603,32 +1635,36 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1636,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1660,33 +1696,37 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1719,32 +1759,36 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -1752,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1776,33 +1820,37 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1835,32 +1883,36 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1868,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1892,17 +1944,17 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1912,17 +1964,17 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1988,7 +2040,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2027,7 +2079,7 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
@@ -2042,7 +2094,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2160,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2147,7 +2199,7 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
@@ -2162,7 +2214,7 @@
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2280,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2344,7 +2396,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2388,13 +2440,17 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2516,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2509,40 +2565,40 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2575,12 +2631,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2594,7 +2650,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2619,46 +2675,50 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2691,12 +2751,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2710,7 +2770,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2735,46 +2795,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2807,12 +2871,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2826,7 +2890,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2851,46 +2915,50 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2923,12 +2991,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2942,7 +3010,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2967,46 +3035,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3039,12 +3111,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3058,7 +3130,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3083,46 +3155,50 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3155,12 +3231,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3174,7 +3250,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3199,46 +3275,50 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3271,12 +3351,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3290,7 +3370,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3315,18 +3395,22 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3339,60 +3423,64 @@
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>117分钟</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3406,7 +3494,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3416,33 +3504,37 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>117.0</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -3455,60 +3547,64 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3522,7 +3618,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3532,33 +3628,37 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3671,7 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3581,7 +3681,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3591,40 +3691,44 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3638,7 +3742,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3648,33 +3752,37 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -3687,60 +3795,64 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>117分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3754,7 +3866,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3764,17 +3876,17 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3784,13 +3896,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>117.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3919,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3813,7 +3929,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3823,40 +3939,44 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>117分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3870,7 +3990,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3880,33 +4000,37 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>117.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -3919,7 +4043,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3929,7 +4053,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3967,12 +4091,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3986,7 +4110,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4022,7 +4146,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4159,7 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -4045,7 +4169,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4083,12 +4207,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4102,7 +4226,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4138,7 +4262,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4275,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4161,7 +4285,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4199,12 +4323,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4218,7 +4342,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4254,7 +4378,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4267,22 +4391,22 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4315,12 +4439,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4334,7 +4458,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4370,7 +4494,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4507,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4393,7 +4517,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4431,12 +4555,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4450,7 +4574,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4486,7 +4610,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4499,22 +4623,22 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4547,12 +4671,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4566,7 +4690,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4602,7 +4726,7 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4615,7 +4739,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4625,7 +4749,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4663,12 +4787,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4682,7 +4806,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4718,7 +4842,7 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4855,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4741,7 +4865,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4779,12 +4903,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4798,7 +4922,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4834,35 +4958,35 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4895,12 +5019,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4914,7 +5038,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4939,7 +5063,7 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -4950,77 +5074,73 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5034,7 +5154,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5044,65 +5164,61 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr">
-        <is>
-          <t>86.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5135,12 +5251,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5154,7 +5270,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5190,77 +5306,73 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5274,7 +5386,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5284,17 +5396,17 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5304,45 +5416,41 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC41" s="2" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5375,12 +5483,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5394,7 +5502,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5430,35 +5538,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5491,12 +5599,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5510,7 +5618,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5546,35 +5654,35 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5607,12 +5715,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5626,7 +5734,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5662,35 +5770,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5723,12 +5831,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5742,7 +5850,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5767,7 +5875,7 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
@@ -5778,35 +5886,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5839,12 +5947,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5858,7 +5966,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5894,35 +6002,35 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5955,12 +6063,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5974,7 +6082,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6010,35 +6118,35 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6071,12 +6179,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6090,47 +6198,3019 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>117.0</t>
+        </is>
+      </c>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>4/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>4/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>117.0</t>
+        </is>
+      </c>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>08:26</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>5/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>3/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
           <t>08:15</t>
         </is>
       </c>
-      <c r="W48" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X48" s="2" t="inlineStr">
+      <c r="X66" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y48" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z48" s="2" t="inlineStr">
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
+      <c r="AA66" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB48" s="2" t="inlineStr">
+      <c r="AB66" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC48" s="2" t="inlineStr">
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
         <is>
           <t>86.0</t>
         </is>
       </c>
-      <c r="AD48" s="2" t="inlineStr">
-        <is>
-          <t>1/9</t>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>5/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>3/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-24-operations.xlsx
+++ b/data/export/2026-10-24-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD73"/>
+  <dimension ref="A1:AD75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -447,10 +447,10 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1769,24 +1769,24 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -2007,32 +2007,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2040,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2064,17 +2068,17 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2084,12 +2088,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
@@ -2160,7 +2164,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2280,7 +2284,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2396,7 +2400,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2516,7 +2520,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2636,7 +2640,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2756,7 +2760,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2876,7 +2880,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2930,7 +2934,7 @@
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2996,7 +3000,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3045,12 +3049,12 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3120,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3236,7 +3240,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3280,12 +3284,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AD23" s="2" t="inlineStr">
@@ -3356,7 +3360,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3480,7 +3484,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3534,7 +3538,7 @@
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3608,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3658,7 +3662,7 @@
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -3728,7 +3732,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3782,7 +3786,7 @@
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -3825,24 +3829,24 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>117分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3852,7 +3856,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3901,12 +3905,12 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>117.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3949,24 +3953,24 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>117分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3976,7 +3980,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4025,12 +4029,12 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>117.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4100,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4146,7 +4150,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4179,32 +4183,36 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4212,7 +4220,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4236,33 +4244,37 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4340,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4378,7 +4390,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4444,7 +4456,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4494,7 +4506,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4572,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4610,7 +4622,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4676,7 +4688,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4726,7 +4738,7 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4759,12 +4771,12 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq41，推进3站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -4792,7 +4804,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4800,10 +4812,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R36" s="2" t="inlineStr"/>
-      <c r="S36" s="2" t="inlineStr"/>
-      <c r="T36" s="2" t="inlineStr"/>
-      <c r="U36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>08:07</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq38（站名待映射） ETA 7分钟参与校验</t>
+        </is>
+      </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -4842,7 +4870,7 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4908,7 +4936,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4958,7 +4986,7 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5024,7 +5052,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5074,7 +5102,7 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5190,7 +5218,7 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5284,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5306,7 +5334,7 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5400,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5422,7 +5450,7 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5488,7 +5516,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5538,7 +5566,7 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5632,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5654,7 +5682,7 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5720,7 +5748,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5770,7 +5798,7 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5864,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5886,7 +5914,7 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5980,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6002,7 +6030,7 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6068,7 +6096,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6118,7 +6146,7 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6212,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6234,7 +6262,7 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6328,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6350,7 +6378,7 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6416,7 +6444,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6466,7 +6494,7 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6532,7 +6560,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6582,7 +6610,7 @@
       <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6648,7 +6676,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6702,7 +6730,7 @@
       </c>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6796,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6822,7 +6850,7 @@
       </c>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6916,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6942,7 +6970,7 @@
       </c>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -6955,22 +6983,22 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -7003,12 +7031,12 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7022,7 +7050,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7047,84 +7075,76 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>117.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7132,7 +7152,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7146,7 +7166,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7156,17 +7176,17 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7181,82 +7201,78 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7270,7 +7286,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7280,17 +7296,17 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7305,12 +7321,12 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -7323,7 +7339,7 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -7333,7 +7349,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -7353,12 +7369,12 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
@@ -7380,7 +7396,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7394,7 +7410,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7429,12 +7445,12 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -7447,7 +7463,7 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -7457,7 +7473,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -7477,19 +7493,19 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7504,7 +7520,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7518,7 +7534,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7553,7 +7569,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
@@ -7571,7 +7587,7 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -7581,7 +7597,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -7591,32 +7607,36 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7624,7 +7644,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7638,7 +7658,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7648,17 +7668,17 @@
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7668,13 +7688,17 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -7687,7 +7711,7 @@
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -7697,7 +7721,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -7717,34 +7741,34 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7758,7 +7782,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7793,12 +7817,12 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>6/12</t>
         </is>
       </c>
     </row>
@@ -7811,7 +7835,7 @@
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -7821,7 +7845,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -7831,40 +7855,44 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7878,7 +7906,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7888,33 +7916,37 @@
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB62" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -7927,7 +7959,7 @@
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -7937,7 +7969,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -7947,32 +7979,36 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr"/>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7980,7 +8016,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7994,7 +8030,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -8004,17 +8040,17 @@
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -8029,12 +8065,12 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -8047,7 +8083,7 @@
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -8057,7 +8093,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -8095,12 +8131,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8114,7 +8150,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8163,7 +8199,7 @@
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -8173,7 +8209,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -8211,12 +8247,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8230,7 +8266,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8255,18 +8291,22 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB65" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -8279,22 +8319,22 @@
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8327,12 +8367,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8346,7 +8386,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8371,22 +8411,18 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC66" s="2" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -8399,22 +8435,22 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8447,12 +8483,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8466,7 +8502,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8491,22 +8527,18 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -8519,22 +8551,22 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8567,12 +8599,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8586,7 +8618,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8621,12 +8653,12 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -8639,22 +8671,22 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8687,12 +8719,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8706,7 +8738,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8731,18 +8763,22 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB69" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>5/12</t>
         </is>
       </c>
     </row>
@@ -8755,7 +8791,7 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -8765,7 +8801,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8803,12 +8839,12 @@
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8822,7 +8858,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8847,18 +8883,22 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB70" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>6/12</t>
         </is>
       </c>
     </row>
@@ -8871,7 +8911,7 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -8881,7 +8921,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8919,12 +8959,12 @@
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8938,7 +8978,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8963,7 +9003,7 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
@@ -8987,7 +9027,7 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -8997,7 +9037,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -9035,12 +9075,12 @@
       <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9054,7 +9094,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9079,22 +9119,18 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC72" s="2" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr"/>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -9107,7 +9143,7 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -9117,7 +9153,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9155,12 +9191,12 @@
       <c r="N73" s="2" t="inlineStr"/>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9174,41 +9210,281 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>3/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="W73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X73" s="2" t="inlineStr">
+      <c r="X74" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y73" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z73" s="2" t="inlineStr">
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB73" s="2" t="inlineStr">
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC73" s="2" t="inlineStr"/>
-      <c r="AD73" s="2" t="inlineStr">
+      <c r="AC75" s="2" t="inlineStr"/>
+      <c r="AD75" s="2" t="inlineStr">
         <is>
           <t>—/12</t>
         </is>

--- a/data/export/2026-10-24-operations.xlsx
+++ b/data/export/2026-10-24-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD75"/>
+  <dimension ref="A1:AD99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -972,17 +972,17 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1091,22 +1091,22 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1215,17 +1215,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1339,22 +1339,22 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1463,22 +1463,22 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -1893,24 +1893,24 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2017,12 +2017,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2093,12 +2093,12 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2131,32 +2131,36 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2164,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2188,17 +2192,17 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2208,17 +2212,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2251,32 +2255,36 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -2284,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2308,33 +2316,37 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2367,32 +2379,36 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2400,7 +2416,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2424,32 +2440,32 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
@@ -2487,32 +2503,36 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2520,7 +2540,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2544,37 +2564,37 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2607,32 +2627,36 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -2640,7 +2664,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2664,37 +2688,37 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2784,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2847,32 +2871,36 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2880,7 +2908,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2904,37 +2932,37 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3028,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3039,7 +3067,7 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -3054,7 +3082,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3148,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3159,7 +3187,7 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
@@ -3174,7 +3202,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3268,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3289,12 +3317,12 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3307,22 +3335,22 @@
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A68870D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3355,12 +3383,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3374,7 +3402,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3399,7 +3427,7 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
@@ -3414,77 +3442,73 @@
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>117分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3498,7 +3522,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3508,107 +3532,103 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>117.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3622,7 +3642,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3632,107 +3652,103 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3746,7 +3762,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3756,107 +3772,103 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3870,7 +3882,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3880,107 +3892,103 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3994,7 +4002,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4004,65 +4012,65 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -4095,12 +4103,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4114,7 +4122,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4139,88 +4147,88 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4234,7 +4242,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4244,22 +4252,22 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
@@ -4269,12 +4277,12 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -4287,60 +4295,64 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>117分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4354,7 +4366,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4364,33 +4376,37 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>117.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -4403,60 +4419,64 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4470,7 +4490,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4480,33 +4500,37 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4543,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4529,7 +4553,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4539,40 +4563,44 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4586,7 +4614,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4596,33 +4624,37 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4635,60 +4667,64 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4702,7 +4738,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4712,33 +4748,37 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4751,7 +4791,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4761,7 +4801,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4771,40 +4811,44 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq41，推进3站，达到≥2站确认条件</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4812,29 +4856,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>物理seq24（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>08:03</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>08:07</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq38（站名待映射） ETA 7分钟参与校验</t>
-        </is>
-      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4844,33 +4872,37 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4883,7 +4915,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4893,7 +4925,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4903,40 +4935,44 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4950,7 +4986,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4960,33 +4996,37 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4999,7 +5039,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -5009,7 +5049,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -5019,40 +5059,44 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5066,7 +5110,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5076,33 +5120,37 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5163,7 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5125,7 +5173,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5135,40 +5183,44 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5182,7 +5234,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5192,33 +5244,37 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -5231,60 +5287,64 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5298,7 +5358,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5308,33 +5368,37 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5411,7 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5357,7 +5421,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5395,12 +5459,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5414,7 +5478,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5439,7 +5503,7 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
@@ -5450,7 +5514,7 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5463,60 +5527,64 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5530,7 +5598,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5540,33 +5608,37 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5651,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5589,7 +5661,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5599,12 +5671,12 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq58，推进20站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -5627,12 +5699,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5640,13 +5712,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr"/>
-      <c r="S43" s="2" t="inlineStr"/>
-      <c r="T43" s="2" t="inlineStr"/>
-      <c r="U43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>08:07</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq38（站名待映射） ETA 7分钟参与校验</t>
+        </is>
+      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5682,7 +5770,7 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5695,7 +5783,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5705,7 +5793,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5715,40 +5803,44 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5762,7 +5854,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5772,17 +5864,17 @@
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5792,13 +5884,17 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC44" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5811,7 +5907,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5821,7 +5917,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5831,40 +5927,44 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5878,7 +5978,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5888,33 +5988,37 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB45" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5927,32 +6031,32 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq39推进至seq56，推进17站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -5975,12 +6079,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5988,13 +6092,25 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R46" s="2" t="inlineStr"/>
-      <c r="S46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
       <c r="T46" s="2" t="inlineStr"/>
-      <c r="U46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq23映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -6030,7 +6146,7 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6159,7 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -6053,7 +6169,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -6091,12 +6207,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6110,7 +6226,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6146,7 +6262,7 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6159,7 +6275,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6169,7 +6285,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6207,12 +6323,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6226,7 +6342,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6262,7 +6378,7 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6275,22 +6391,22 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6323,12 +6439,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6342,7 +6458,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6378,7 +6494,7 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6391,7 +6507,7 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6401,7 +6517,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6439,12 +6555,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6458,7 +6574,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6494,7 +6610,7 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6507,7 +6623,7 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -6517,7 +6633,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -6555,12 +6671,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6574,7 +6690,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6610,7 +6726,7 @@
       <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6623,7 +6739,7 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -6633,7 +6749,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -6671,12 +6787,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6690,7 +6806,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6715,22 +6831,18 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr">
-        <is>
-          <t>117.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6855,7 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -6753,7 +6865,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6791,12 +6903,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6810,7 +6922,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6835,22 +6947,18 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC53" s="2" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6863,7 +6971,7 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -6873,7 +6981,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -6916,7 +7024,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6930,7 +7038,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6955,22 +7063,18 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6983,22 +7087,22 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>08:48</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -7031,12 +7135,12 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7050,7 +7154,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7086,7 +7190,7 @@
       <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -7099,22 +7203,22 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -7147,12 +7251,12 @@
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7166,7 +7270,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7191,22 +7295,18 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>123.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -7219,22 +7319,22 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -7272,7 +7372,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7286,7 +7386,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7311,84 +7411,76 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr">
-        <is>
-          <t>124.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7396,7 +7488,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7410,7 +7502,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7420,107 +7512,99 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr"/>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7534,7 +7618,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7544,17 +7628,17 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7569,74 +7653,70 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>117.0</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7644,7 +7724,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7658,7 +7738,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7668,17 +7748,17 @@
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7693,82 +7773,78 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7782,7 +7858,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7792,17 +7868,17 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7817,82 +7893,78 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7906,7 +7978,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7916,99 +7988,91 @@
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr">
-        <is>
-          <t>83.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr"/>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr"/>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8016,7 +8080,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8030,7 +8094,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -8040,17 +8104,17 @@
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -8065,40 +8129,40 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -8131,12 +8195,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8150,7 +8214,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8175,46 +8239,50 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB64" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8247,12 +8315,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8266,7 +8334,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8301,40 +8369,40 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8367,12 +8435,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8386,7 +8454,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8411,46 +8479,50 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB66" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8483,12 +8555,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8502,7 +8574,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8527,46 +8599,50 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8599,12 +8675,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8618,7 +8694,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8653,40 +8729,40 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8719,12 +8795,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8738,7 +8814,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8763,50 +8839,46 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC69" s="2" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8839,12 +8911,12 @@
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8858,7 +8930,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8888,45 +8960,41 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC70" s="2" t="inlineStr">
-        <is>
-          <t>86.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr"/>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8959,12 +9027,12 @@
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8978,7 +9046,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -9003,46 +9071,50 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB71" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -9075,12 +9147,12 @@
       <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9094,7 +9166,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9119,18 +9191,22 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB72" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -9143,52 +9219,56 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9196,7 +9276,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9210,7 +9290,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9220,37 +9300,37 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB73" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -9263,60 +9343,64 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9330,7 +9414,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9340,22 +9424,22 @@
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
@@ -9365,12 +9449,12 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -9383,60 +9467,64 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9450,43 +9538,2923 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>08:26</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="W75" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X75" s="2" t="inlineStr">
+      <c r="X89" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y75" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z75" s="2" t="inlineStr">
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB75" s="2" t="inlineStr">
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC75" s="2" t="inlineStr"/>
-      <c r="AD75" s="2" t="inlineStr">
-        <is>
-          <t>—/12</t>
+      <c r="AC90" s="2" t="inlineStr"/>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr"/>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr"/>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr"/>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD96" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr"/>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD97" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr"/>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD98" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr"/>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AD99" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-24-operations.xlsx
+++ b/data/export/2026-10-24-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD31" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AD34" s="2" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5436,12 +5436,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD51" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7292,12 +7292,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7912,12 +7912,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
@@ -8860,7 +8860,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8984,7 +8984,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -9232,7 +9232,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
@@ -9577,24 +9577,24 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
@@ -9701,24 +9701,24 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
@@ -9728,7 +9728,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9777,7 +9777,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9939,32 +9939,36 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9972,7 +9976,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9996,17 +10000,17 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -10016,7 +10020,7 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -10059,32 +10063,36 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -10092,7 +10100,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10116,17 +10124,17 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -10136,12 +10144,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
@@ -10179,32 +10187,36 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:38</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -10212,7 +10224,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10236,17 +10248,17 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -10256,12 +10268,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
@@ -10332,7 +10344,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10381,7 +10393,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
@@ -10452,7 +10464,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10496,7 +10508,7 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10824,7 +10836,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10868,17 +10880,17 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -11196,7 +11208,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -11250,7 +11262,7 @@
       </c>
       <c r="AD87" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11386,7 @@
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -11498,7 +11510,7 @@
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11700,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11742,7 +11754,7 @@
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -11812,7 +11824,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11856,17 +11868,17 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12014,7 @@
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12138,7 @@
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -12196,7 +12208,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12240,17 +12252,17 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -12316,7 +12328,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12448,7 +12460,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12492,17 +12504,17 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -12572,7 +12584,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12626,7 +12638,7 @@
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -12750,7 +12762,7 @@
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -12820,7 +12832,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -12864,17 +12876,17 @@
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -12940,7 +12952,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -13064,7 +13076,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -13242,7 +13254,7 @@
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -13312,7 +13324,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -13361,7 +13373,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AD104" s="2" t="inlineStr">
@@ -13490,7 +13502,7 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -13560,7 +13572,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -13614,7 +13626,7 @@
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -13684,7 +13696,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13728,17 +13740,17 @@
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -13862,7 +13874,7 @@
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -14176,7 +14188,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14220,17 +14232,17 @@
       </c>
       <c r="AB111" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC111" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -14664,7 +14676,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -14718,7 +14730,7 @@
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -14842,7 +14854,7 @@
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -14966,7 +14978,7 @@
       </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -15292,7 +15304,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15346,7 +15358,7 @@
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -15416,7 +15428,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -15460,17 +15472,17 @@
       </c>
       <c r="AB121" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC121" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -15594,7 +15606,7 @@
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -15664,7 +15676,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15708,17 +15720,17 @@
       </c>
       <c r="AB123" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC123" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -15788,7 +15800,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15842,7 +15854,7 @@
       </c>
       <c r="AD124" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -15912,7 +15924,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -15956,17 +15968,17 @@
       </c>
       <c r="AB125" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC125" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -16090,7 +16102,7 @@
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -16160,7 +16172,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -16204,17 +16216,17 @@
       </c>
       <c r="AB127" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC127" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -16284,7 +16296,7 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -16462,7 +16474,7 @@
       </c>
       <c r="AD129" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -16532,7 +16544,7 @@
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -16656,7 +16668,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -16710,7 +16722,7 @@
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16846,7 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -17330,7 +17342,7 @@
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -17710,7 +17722,7 @@
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -17834,7 +17846,7 @@
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -17904,7 +17916,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -18082,7 +18094,7 @@
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -18152,7 +18164,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18196,17 +18208,17 @@
       </c>
       <c r="AB143" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC143" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -18330,7 +18342,7 @@
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -18400,7 +18412,7 @@
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
@@ -18698,7 +18710,7 @@
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -19070,7 +19082,7 @@
       </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -19194,7 +19206,7 @@
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -19260,7 +19272,7 @@
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr">
@@ -19304,17 +19316,17 @@
       </c>
       <c r="AB152" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC152" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -19562,7 +19574,7 @@
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -19632,7 +19644,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -19676,17 +19688,17 @@
       </c>
       <c r="AB155" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC155" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -19756,7 +19768,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19805,7 +19817,7 @@
       </c>
       <c r="AC156" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AD156" s="2" t="inlineStr">
@@ -19880,7 +19892,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19924,17 +19936,17 @@
       </c>
       <c r="AB157" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC157" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -20004,7 +20016,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -20048,17 +20060,17 @@
       </c>
       <c r="AB158" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC158" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -20128,7 +20140,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20252,7 +20264,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -20306,7 +20318,7 @@
       </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -20376,7 +20388,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q161" s="2" t="inlineStr">
@@ -20420,17 +20432,17 @@
       </c>
       <c r="AB161" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC161" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -20620,7 +20632,7 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q163" s="2" t="inlineStr">
@@ -20674,7 +20686,7 @@
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -20744,7 +20756,7 @@
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q164" s="2" t="inlineStr">
@@ -20798,7 +20810,7 @@
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -21042,7 +21054,7 @@
       </c>
       <c r="AD166" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -21290,7 +21302,7 @@
       </c>
       <c r="AD168" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -21360,7 +21372,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -21414,7 +21426,7 @@
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -21538,7 +21550,7 @@
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -21662,7 +21674,7 @@
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -21782,7 +21794,7 @@
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -21976,7 +21988,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22073,24 +22085,24 @@
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="2" t="inlineStr"/>
       <c r="M175" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N175" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O175" s="2" t="inlineStr">
@@ -22100,7 +22112,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22149,7 +22161,7 @@
       </c>
       <c r="AC175" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AD175" s="2" t="inlineStr">
@@ -22187,32 +22199,36 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="2" t="inlineStr"/>
       <c r="M176" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N176" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O176" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -22220,7 +22236,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22244,17 +22260,17 @@
       </c>
       <c r="X176" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y176" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z176" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA176" s="2" t="inlineStr">
@@ -22264,17 +22280,17 @@
       </c>
       <c r="AB176" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC176" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -22307,32 +22323,36 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="2" t="inlineStr"/>
       <c r="M177" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N177" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O177" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -22340,7 +22360,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22364,17 +22384,17 @@
       </c>
       <c r="X177" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z177" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA177" s="2" t="inlineStr">
@@ -22384,17 +22404,17 @@
       </c>
       <c r="AB177" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC177" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -22427,32 +22447,36 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="2" t="inlineStr"/>
       <c r="M178" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N178" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O178" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -22460,7 +22484,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22484,17 +22508,17 @@
       </c>
       <c r="X178" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y178" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z178" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA178" s="2" t="inlineStr">
@@ -22504,17 +22528,17 @@
       </c>
       <c r="AB178" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC178" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -22552,7 +22576,7 @@
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq30，推进2站，达到≥2站确认条件</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq59，推进31站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr">
@@ -22580,7 +22604,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22650,7 +22674,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -22683,32 +22707,36 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr"/>
       <c r="L180" s="2" t="inlineStr"/>
       <c r="M180" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N180" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O180" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -22716,7 +22744,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22740,17 +22768,17 @@
       </c>
       <c r="X180" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z180" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA180" s="2" t="inlineStr">
@@ -22760,17 +22788,17 @@
       </c>
       <c r="AB180" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC180" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -22803,32 +22831,36 @@
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K181" s="2" t="inlineStr"/>
       <c r="L181" s="2" t="inlineStr"/>
       <c r="M181" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N181" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O181" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -22836,7 +22868,7 @@
       </c>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q181" s="2" t="inlineStr">
@@ -22860,17 +22892,17 @@
       </c>
       <c r="X181" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z181" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA181" s="2" t="inlineStr">
@@ -22880,17 +22912,17 @@
       </c>
       <c r="AB181" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC181" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -22956,7 +22988,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -23076,7 +23108,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23130,7 +23162,7 @@
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -23163,32 +23195,36 @@
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K184" s="2" t="inlineStr"/>
       <c r="L184" s="2" t="inlineStr"/>
       <c r="M184" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N184" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N184" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O184" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -23196,7 +23232,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -23220,17 +23256,17 @@
       </c>
       <c r="X184" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y184" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z184" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA184" s="2" t="inlineStr">
@@ -23240,17 +23276,17 @@
       </c>
       <c r="AB184" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC184" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -23316,7 +23352,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -23436,7 +23472,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23490,7 +23526,7 @@
       </c>
       <c r="AD186" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -23556,7 +23592,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q187" s="2" t="inlineStr">
@@ -23610,7 +23646,7 @@
       </c>
       <c r="AD187" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -23676,7 +23712,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q188" s="2" t="inlineStr">
@@ -24102,7 +24138,7 @@
       </c>
       <c r="AD191" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -24420,7 +24456,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24469,12 +24505,12 @@
       </c>
       <c r="AC194" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AD194" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -24788,7 +24824,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24837,12 +24873,12 @@
       </c>
       <c r="AC197" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -24912,7 +24948,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -24956,17 +24992,17 @@
       </c>
       <c r="AB198" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC198" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -25090,7 +25126,7 @@
       </c>
       <c r="AD199" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -25396,7 +25432,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25440,12 +25476,12 @@
       </c>
       <c r="AB202" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC202" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AD202" s="2" t="inlineStr">
@@ -25768,7 +25804,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25817,12 +25853,12 @@
       </c>
       <c r="AC205" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AD205" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -25892,7 +25928,7 @@
       </c>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q206" s="2" t="inlineStr">
@@ -25936,17 +25972,17 @@
       </c>
       <c r="AB206" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC206" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -26016,7 +26052,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q207" s="2" t="inlineStr">
@@ -26060,17 +26096,17 @@
       </c>
       <c r="AB207" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC207" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AD207" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -26140,7 +26176,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q208" s="2" t="inlineStr">
@@ -26184,17 +26220,17 @@
       </c>
       <c r="AB208" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC208" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AD208" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -26512,7 +26548,7 @@
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q211" s="2" t="inlineStr">
@@ -26561,12 +26597,12 @@
       </c>
       <c r="AC211" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AD211" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -26756,7 +26792,7 @@
       </c>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q213" s="2" t="inlineStr">
@@ -26800,17 +26836,17 @@
       </c>
       <c r="AB213" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC213" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD213" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27090,7 @@
       </c>
       <c r="AD215" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -27248,7 +27284,7 @@
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q217" s="2" t="inlineStr">
@@ -27292,12 +27328,12 @@
       </c>
       <c r="AB217" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC217" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AD217" s="2" t="inlineStr">
@@ -27368,7 +27404,7 @@
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q218" s="2" t="inlineStr">
@@ -27417,12 +27453,12 @@
       </c>
       <c r="AC218" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AD218" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -27492,7 +27528,7 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q219" s="2" t="inlineStr">
@@ -27536,17 +27572,17 @@
       </c>
       <c r="AB219" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC219" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AD219" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -27616,7 +27652,7 @@
       </c>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q220" s="2" t="inlineStr">
@@ -27660,17 +27696,17 @@
       </c>
       <c r="AB220" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC220" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AD220" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -27864,7 +27900,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q222" s="2" t="inlineStr">
@@ -27908,17 +27944,17 @@
       </c>
       <c r="AB222" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC222" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AD222" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -27988,7 +28024,7 @@
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q223" s="2" t="inlineStr">
@@ -28032,17 +28068,17 @@
       </c>
       <c r="AB223" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC223" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD223" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -28166,7 +28202,7 @@
       </c>
       <c r="AD224" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -28356,7 +28392,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q226" s="2" t="inlineStr">
@@ -28400,12 +28436,12 @@
       </c>
       <c r="AB226" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC226" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AD226" s="2" t="inlineStr">
@@ -28604,7 +28640,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q228" s="2" t="inlineStr">
@@ -28648,17 +28684,17 @@
       </c>
       <c r="AB228" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC228" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AD228" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -28852,7 +28888,7 @@
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q230" s="2" t="inlineStr">
@@ -28896,17 +28932,17 @@
       </c>
       <c r="AB230" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC230" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AD230" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -28976,7 +29012,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q231" s="2" t="inlineStr">
@@ -29020,17 +29056,17 @@
       </c>
       <c r="AB231" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC231" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AD231" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -29224,7 +29260,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q233" s="2" t="inlineStr">
@@ -29268,17 +29304,17 @@
       </c>
       <c r="AB233" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC233" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AD233" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -29844,7 +29880,7 @@
       </c>
       <c r="P238" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q238" s="2" t="inlineStr">
@@ -29888,17 +29924,17 @@
       </c>
       <c r="AB238" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC238" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AD238" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -29968,7 +30004,7 @@
       </c>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q239" s="2" t="inlineStr">
@@ -30017,12 +30053,12 @@
       </c>
       <c r="AC239" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AD239" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -30092,7 +30128,7 @@
       </c>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q240" s="2" t="inlineStr">
@@ -30136,17 +30172,17 @@
       </c>
       <c r="AB240" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC240" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD240" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -30216,7 +30252,7 @@
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q241" s="2" t="inlineStr">
@@ -30260,17 +30296,17 @@
       </c>
       <c r="AB241" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC241" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AD241" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -30712,7 +30748,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q245" s="2" t="inlineStr">
@@ -30756,12 +30792,12 @@
       </c>
       <c r="AB245" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC245" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AD245" s="2" t="inlineStr">
@@ -30960,7 +30996,7 @@
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q247" s="2" t="inlineStr">
@@ -31004,17 +31040,17 @@
       </c>
       <c r="AB247" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC247" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AD247" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -31208,7 +31244,7 @@
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q249" s="2" t="inlineStr">
@@ -31257,12 +31293,12 @@
       </c>
       <c r="AC249" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AD249" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -31332,7 +31368,7 @@
       </c>
       <c r="P250" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q250" s="2" t="inlineStr">
@@ -31381,12 +31417,12 @@
       </c>
       <c r="AC250" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AD250" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -31456,7 +31492,7 @@
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q251" s="2" t="inlineStr">
@@ -31500,17 +31536,17 @@
       </c>
       <c r="AB251" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC251" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD251" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -31580,7 +31616,7 @@
       </c>
       <c r="P252" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q252" s="2" t="inlineStr">
@@ -31624,17 +31660,17 @@
       </c>
       <c r="AB252" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC252" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AD252" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -31704,7 +31740,7 @@
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q253" s="2" t="inlineStr">
@@ -31748,17 +31784,17 @@
       </c>
       <c r="AB253" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC253" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AD253" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -31948,7 +31984,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q255" s="2" t="inlineStr">
@@ -31992,17 +32028,17 @@
       </c>
       <c r="AB255" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC255" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AD255" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -32122,7 +32158,7 @@
       </c>
       <c r="AD256" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -32436,7 +32472,7 @@
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q259" s="2" t="inlineStr">
@@ -32480,12 +32516,12 @@
       </c>
       <c r="AB259" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC259" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AD259" s="2" t="inlineStr">
@@ -32680,7 +32716,7 @@
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q261" s="2" t="inlineStr">
@@ -32724,17 +32760,17 @@
       </c>
       <c r="AB261" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC261" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -33052,7 +33088,7 @@
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q264" s="2" t="inlineStr">
@@ -33101,12 +33137,12 @@
       </c>
       <c r="AC264" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AD264" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -33176,7 +33212,7 @@
       </c>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q265" s="2" t="inlineStr">
@@ -33225,12 +33261,12 @@
       </c>
       <c r="AC265" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AD265" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -33300,7 +33336,7 @@
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q266" s="2" t="inlineStr">
@@ -33344,17 +33380,17 @@
       </c>
       <c r="AB266" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC266" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AD266" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -33420,7 +33456,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q267" s="2" t="inlineStr">
@@ -33464,17 +33500,17 @@
       </c>
       <c r="AB267" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC267" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AD267" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -33544,7 +33580,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q268" s="2" t="inlineStr">
@@ -33588,17 +33624,17 @@
       </c>
       <c r="AB268" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC268" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD268" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -33668,7 +33704,7 @@
       </c>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q269" s="2" t="inlineStr">
@@ -33712,17 +33748,17 @@
       </c>
       <c r="AB269" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC269" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AD269" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -33846,7 +33882,7 @@
       </c>
       <c r="AD270" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -34280,7 +34316,7 @@
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q274" s="2" t="inlineStr">
@@ -34324,12 +34360,12 @@
       </c>
       <c r="AB274" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC274" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AD274" s="2" t="inlineStr">
@@ -34528,7 +34564,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q276" s="2" t="inlineStr">
@@ -34572,17 +34608,17 @@
       </c>
       <c r="AB276" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC276" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -34873,24 +34909,24 @@
       </c>
       <c r="I279" s="2" t="inlineStr">
         <is>
-          <t>20:36</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="J279" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K279" s="2" t="inlineStr"/>
       <c r="L279" s="2" t="inlineStr"/>
       <c r="M279" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N279" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O279" s="2" t="inlineStr">
@@ -34900,7 +34936,7 @@
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q279" s="2" t="inlineStr">
@@ -34949,12 +34985,12 @@
       </c>
       <c r="AC279" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AD279" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -34997,24 +35033,24 @@
       </c>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="J280" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K280" s="2" t="inlineStr"/>
       <c r="L280" s="2" t="inlineStr"/>
       <c r="M280" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N280" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O280" s="2" t="inlineStr">
@@ -35024,7 +35060,7 @@
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q280" s="2" t="inlineStr">
@@ -35073,12 +35109,12 @@
       </c>
       <c r="AC280" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AD280" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -35111,32 +35147,36 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I281" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:48</t>
         </is>
       </c>
       <c r="J281" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K281" s="2" t="inlineStr"/>
       <c r="L281" s="2" t="inlineStr"/>
       <c r="M281" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N281" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N281" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O281" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -35144,7 +35184,7 @@
       </c>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q281" s="2" t="inlineStr">
@@ -35168,17 +35208,17 @@
       </c>
       <c r="X281" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y281" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z281" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA281" s="2" t="inlineStr">
@@ -35188,17 +35228,17 @@
       </c>
       <c r="AB281" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC281" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AD281" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -35318,7 +35358,7 @@
       </c>
       <c r="AD282" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -35471,32 +35511,36 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K284" s="2" t="inlineStr"/>
       <c r="L284" s="2" t="inlineStr"/>
       <c r="M284" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N284" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N284" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O284" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -35504,7 +35548,7 @@
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q284" s="2" t="inlineStr">
@@ -35528,17 +35572,17 @@
       </c>
       <c r="X284" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y284" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z284" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA284" s="2" t="inlineStr">
@@ -35548,17 +35592,17 @@
       </c>
       <c r="AB284" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC284" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD284" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -35591,32 +35635,36 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="J285" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K285" s="2" t="inlineStr"/>
       <c r="L285" s="2" t="inlineStr"/>
       <c r="M285" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N285" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N285" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O285" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -35624,7 +35672,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35648,17 +35696,17 @@
       </c>
       <c r="X285" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y285" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z285" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA285" s="2" t="inlineStr">
@@ -35668,17 +35716,17 @@
       </c>
       <c r="AB285" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC285" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AD285" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -35711,32 +35759,36 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:16</t>
         </is>
       </c>
       <c r="J286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K286" s="2" t="inlineStr"/>
       <c r="L286" s="2" t="inlineStr"/>
       <c r="M286" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N286" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N286" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O286" s="2" t="inlineStr">
         <is>
           <t>12:01</t>
@@ -35744,7 +35796,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -35768,17 +35820,17 @@
       </c>
       <c r="X286" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z286" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA286" s="2" t="inlineStr">
@@ -35788,17 +35840,17 @@
       </c>
       <c r="AB286" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC286" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AD286" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -35831,32 +35883,36 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I287" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:29</t>
         </is>
       </c>
       <c r="J287" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K287" s="2" t="inlineStr"/>
       <c r="L287" s="2" t="inlineStr"/>
       <c r="M287" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N287" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N287" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O287" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -35864,7 +35920,7 @@
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q287" s="2" t="inlineStr">
@@ -35888,17 +35944,17 @@
       </c>
       <c r="X287" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y287" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z287" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA287" s="2" t="inlineStr">
@@ -35908,12 +35964,12 @@
       </c>
       <c r="AB287" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC287" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AD287" s="2" t="inlineStr">
@@ -35951,32 +36007,36 @@
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:55</t>
         </is>
       </c>
       <c r="J288" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="2" t="inlineStr"/>
       <c r="M288" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N288" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N288" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O288" s="2" t="inlineStr">
         <is>
           <t>08:21</t>
@@ -35984,7 +36044,7 @@
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q288" s="2" t="inlineStr">
@@ -36008,17 +36068,17 @@
       </c>
       <c r="X288" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y288" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z288" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA288" s="2" t="inlineStr">
@@ -36028,17 +36088,17 @@
       </c>
       <c r="AB288" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC288" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AD288" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -36104,7 +36164,7 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q289" s="2" t="inlineStr">
@@ -36148,17 +36208,17 @@
       </c>
       <c r="AB289" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC289" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AD289" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -36224,7 +36284,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q290" s="2" t="inlineStr">
@@ -36268,17 +36328,17 @@
       </c>
       <c r="AB290" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC290" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AD290" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-24-operations.xlsx
+++ b/data/export/2026-10-24-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,12 +724,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1468,17 +1468,17 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1964,12 +1964,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2956,17 +2956,17 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3948,17 +3948,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6424,12 +6424,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7664,17 +7664,17 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -8736,7 +8736,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8780,17 +8780,17 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -8860,7 +8860,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -9728,7 +9728,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9772,17 +9772,17 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -9976,7 +9976,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
@@ -10197,19 +10197,19 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>21:38</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>68分钟</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -10224,7 +10224,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
@@ -10311,32 +10311,36 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:07</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10344,7 +10348,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10368,17 +10372,17 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -10388,17 +10392,17 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -10431,32 +10435,36 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10464,7 +10472,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10488,17 +10496,17 @@
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
@@ -10508,12 +10516,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AD81" s="2" t="inlineStr">
@@ -10890,7 +10898,7 @@
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -11014,7 +11022,7 @@
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -11138,7 +11146,7 @@
       </c>
       <c r="AD86" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -11262,7 +11270,7 @@
       </c>
       <c r="AD87" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -11510,7 +11518,7 @@
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -11634,7 +11642,7 @@
       </c>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -11700,7 +11708,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11744,17 +11752,17 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -11878,7 +11886,7 @@
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -12014,7 +12022,7 @@
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -12138,7 +12146,7 @@
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -12584,7 +12592,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12638,7 +12646,7 @@
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -12832,7 +12840,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -12952,7 +12960,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -13006,7 +13014,7 @@
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -13076,7 +13084,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -13120,17 +13128,17 @@
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>131.2</t>
         </is>
       </c>
       <c r="AD102" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -13378,7 +13386,7 @@
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -13626,7 +13634,7 @@
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -13750,7 +13758,7 @@
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -13874,7 +13882,7 @@
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -14242,7 +14250,7 @@
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -14482,7 +14490,7 @@
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -14606,7 +14614,7 @@
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -14730,7 +14738,7 @@
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -14978,7 +14986,7 @@
       </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -15102,7 +15110,7 @@
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -15304,7 +15312,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15348,17 +15356,17 @@
       </c>
       <c r="AB120" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC120" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -15482,7 +15490,7 @@
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -15606,7 +15614,7 @@
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -15800,7 +15808,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15854,7 +15862,7 @@
       </c>
       <c r="AD124" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -16172,7 +16180,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -16296,7 +16304,7 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -16350,7 +16358,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -16544,7 +16552,7 @@
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -16588,17 +16596,17 @@
       </c>
       <c r="AB130" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC130" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>131.2</t>
         </is>
       </c>
       <c r="AD130" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -16722,7 +16730,7 @@
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -16846,7 +16854,7 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -17094,7 +17102,7 @@
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -17218,7 +17226,7 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -17342,7 +17350,7 @@
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17606,7 @@
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -17722,7 +17730,7 @@
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -17846,7 +17854,7 @@
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -18412,7 +18420,7 @@
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
@@ -18456,17 +18464,17 @@
       </c>
       <c r="AB145" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC145" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>131.2</t>
         </is>
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -18710,7 +18718,7 @@
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -18958,7 +18966,7 @@
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -19206,7 +19214,7 @@
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -19326,7 +19334,7 @@
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -19574,7 +19582,7 @@
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -19822,7 +19830,7 @@
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -19946,7 +19954,7 @@
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -20016,7 +20024,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -20318,7 +20326,7 @@
       </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -20442,7 +20450,7 @@
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -20566,7 +20574,7 @@
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -20686,7 +20694,7 @@
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -20756,7 +20764,7 @@
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q164" s="2" t="inlineStr">
@@ -20800,17 +20808,17 @@
       </c>
       <c r="AB164" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC164" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -20934,7 +20942,7 @@
       </c>
       <c r="AD165" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -21054,7 +21062,7 @@
       </c>
       <c r="AD166" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -21372,7 +21380,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -21426,7 +21434,7 @@
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -21794,7 +21802,7 @@
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -21988,7 +21996,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22042,7 +22050,7 @@
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -22166,7 +22174,7 @@
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -22414,7 +22422,7 @@
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -22538,7 +22546,7 @@
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -22674,7 +22682,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -22798,7 +22806,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -23162,7 +23170,7 @@
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -23232,7 +23240,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -23319,32 +23327,36 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:05</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K185" s="2" t="inlineStr"/>
       <c r="L185" s="2" t="inlineStr"/>
       <c r="M185" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N185" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N185" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O185" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -23352,7 +23364,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -23376,17 +23388,17 @@
       </c>
       <c r="X185" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z185" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA185" s="2" t="inlineStr">
@@ -23396,17 +23408,17 @@
       </c>
       <c r="AB185" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC185" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>131.2</t>
         </is>
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -23439,32 +23451,36 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:04</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>119分钟</t>
         </is>
       </c>
       <c r="K186" s="2" t="inlineStr"/>
       <c r="L186" s="2" t="inlineStr"/>
       <c r="M186" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N186" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N186" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O186" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -23472,7 +23488,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23496,17 +23512,17 @@
       </c>
       <c r="X186" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y186" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z186" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA186" s="2" t="inlineStr">
@@ -23516,17 +23532,17 @@
       </c>
       <c r="AB186" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC186" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AD186" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -23592,7 +23608,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q187" s="2" t="inlineStr">
@@ -23646,7 +23662,7 @@
       </c>
       <c r="AD187" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -23712,7 +23728,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q188" s="2" t="inlineStr">
@@ -23766,7 +23782,7 @@
       </c>
       <c r="AD188" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -23890,7 +23906,7 @@
       </c>
       <c r="AD189" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -24754,7 +24770,7 @@
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -25928,7 +25944,7 @@
       </c>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q206" s="2" t="inlineStr">
@@ -25977,12 +25993,12 @@
       </c>
       <c r="AC206" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -26052,7 +26068,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q207" s="2" t="inlineStr">
@@ -26096,17 +26112,17 @@
       </c>
       <c r="AB207" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC207" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AD207" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -26478,7 +26494,7 @@
       </c>
       <c r="AD210" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -27652,7 +27668,7 @@
       </c>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q220" s="2" t="inlineStr">
@@ -27701,12 +27717,12 @@
       </c>
       <c r="AC220" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD220" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -27830,7 +27846,7 @@
       </c>
       <c r="AD221" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -27900,7 +27916,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q222" s="2" t="inlineStr">
@@ -27944,17 +27960,17 @@
       </c>
       <c r="AB222" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC222" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AD222" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -28640,7 +28656,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q228" s="2" t="inlineStr">
@@ -28689,12 +28705,12 @@
       </c>
       <c r="AC228" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD228" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -28888,7 +28904,7 @@
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q230" s="2" t="inlineStr">
@@ -28932,17 +28948,17 @@
       </c>
       <c r="AB230" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC230" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AD230" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -29260,7 +29276,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q233" s="2" t="inlineStr">
@@ -30252,7 +30268,7 @@
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q241" s="2" t="inlineStr">
@@ -30996,7 +31012,7 @@
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q247" s="2" t="inlineStr">
@@ -31045,12 +31061,12 @@
       </c>
       <c r="AC247" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD247" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -31740,7 +31756,7 @@
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q253" s="2" t="inlineStr">
@@ -31784,17 +31800,17 @@
       </c>
       <c r="AB253" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC253" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AD253" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -31984,7 +32000,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q255" s="2" t="inlineStr">
@@ -32402,7 +32418,7 @@
       </c>
       <c r="AD258" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -32716,7 +32732,7 @@
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q261" s="2" t="inlineStr">
@@ -32765,12 +32781,12 @@
       </c>
       <c r="AC261" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -33456,7 +33472,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q267" s="2" t="inlineStr">
@@ -33500,17 +33516,17 @@
       </c>
       <c r="AB267" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC267" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AD267" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -33704,7 +33720,7 @@
       </c>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q269" s="2" t="inlineStr">
@@ -34126,7 +34142,7 @@
       </c>
       <c r="AD272" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -34564,7 +34580,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q276" s="2" t="inlineStr">
@@ -34613,12 +34629,12 @@
       </c>
       <c r="AC276" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -35478,7 +35494,7 @@
       </c>
       <c r="AD283" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -35672,7 +35688,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35716,17 +35732,17 @@
       </c>
       <c r="AB285" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC285" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AD285" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -35796,7 +35812,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -36017,24 +36033,24 @@
       </c>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>21:55</t>
+          <t>21:56</t>
         </is>
       </c>
       <c r="J288" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="2" t="inlineStr"/>
       <c r="M288" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N288" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O288" s="2" t="inlineStr">
@@ -36044,7 +36060,7 @@
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q288" s="2" t="inlineStr">
@@ -36093,12 +36109,12 @@
       </c>
       <c r="AC288" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD288" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -36131,32 +36147,36 @@
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I289" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:27</t>
         </is>
       </c>
       <c r="J289" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K289" s="2" t="inlineStr"/>
       <c r="L289" s="2" t="inlineStr"/>
       <c r="M289" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N289" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N289" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O289" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -36164,7 +36184,7 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q289" s="2" t="inlineStr">
@@ -36188,17 +36208,17 @@
       </c>
       <c r="X289" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y289" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z289" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA289" s="2" t="inlineStr">
@@ -36208,17 +36228,17 @@
       </c>
       <c r="AB289" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC289" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AD289" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -36284,7 +36304,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q290" s="2" t="inlineStr">

--- a/data/export/2026-10-24-operations.xlsx
+++ b/data/export/2026-10-24-operations.xlsx
@@ -29276,7 +29276,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>21:51</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="Q233" s="2" t="inlineStr">
@@ -30268,7 +30268,7 @@
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>21:51</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="Q241" s="2" t="inlineStr">
@@ -32000,7 +32000,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>21:51</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="Q255" s="2" t="inlineStr">
@@ -33720,7 +33720,7 @@
       </c>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>21:51</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="Q269" s="2" t="inlineStr">
@@ -35812,7 +35812,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>21:51</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -36304,7 +36304,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>21:51</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="Q290" s="2" t="inlineStr">
